--- a/vse-loti/341283056/spec-341283056.xlsx
+++ b/vse-loti/341283056/spec-341283056.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,6 +98,9 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -468,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -561,7 +564,7 @@
         <v>200490</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>240588</v>
+        <v>244597.8</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +599,7 @@
         <v>200490.01</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>240588.01</v>
+        <v>244597.81</v>
       </c>
     </row>
     <row r="4">
@@ -631,7 +634,7 @@
         <v>126010</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>151212</v>
+        <v>153732.2</v>
       </c>
     </row>
     <row r="5">
@@ -666,7 +669,7 @@
         <v>146400</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>175680</v>
+        <v>178608</v>
       </c>
     </row>
     <row r="6">
@@ -693,7 +696,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>НМЦК с НДС 22% (справочно):</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>1811111.08</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Трубная часть лота: 4 из 9 позиций; остальное — не трубы (сталь, стальной, швеллер, …), в таблицу не включено. ИТОГО — только трубная часть, «НМЦК из обоснования» — весь лот. Доля трубной части в НМЦК: 33.31 %.</t>
         </is>
@@ -702,15 +715,22 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
+          <t>Ставка НДС в документах не указана, расчёт справочный по 22 %; закупка по 223-ФЗ, включать налоги в цену закон не требует — суммы взяты как в документе («без НДС»). «без НДС» — сумма из документа, «с НДС» = сумма × 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
           <t>Источник: 10188 Извещение.docx</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:B12"/>
+    <mergeCell ref="A12:B14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341283056/spec-341283056.xlsx
+++ b/vse-loti/341283056/spec-341283056.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -483,6 +483,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -518,17 +519,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -558,13 +564,16 @@
         <v>0.544</v>
       </c>
       <c r="G2" s="5" t="n">
+        <v>200490</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>109066.56</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>200490</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>244597.8</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>133061.2</v>
       </c>
     </row>
     <row r="3">
@@ -593,13 +602,16 @@
         <v>0.3782</v>
       </c>
       <c r="G3" s="5" t="n">
+        <v>200490.01</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>75825.32000000001</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>200490.01</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>244597.81</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>92506.89</v>
       </c>
     </row>
     <row r="4">
@@ -628,13 +640,16 @@
         <v>0.168</v>
       </c>
       <c r="G4" s="5" t="n">
+        <v>126010</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>21169.68</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>126010</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>153732.2</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>25827.01</v>
       </c>
     </row>
     <row r="5">
@@ -663,74 +678,232 @@
         <v>1.9701</v>
       </c>
       <c r="G5" s="5" t="n">
+        <v>146400</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>288422.64</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>146400</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>178608</v>
       </c>
+      <c r="J5" s="5" t="n">
+        <v>351875.62</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n">
+          <t>Прочие позиции лота (5) — не трубы, в трубную часть и в цену за тонну не входят</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Сталь листовая 6,0 мм Ст.3 1500х6000, 6,0 мм Ст.3 1500х6000 (423,9 кг)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="6" t="n">
+        <v>423.9</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>82423.12</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>100556.21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Сталь угловая 50*50, 50*50*5 сталь 3сп5, L = 6м -22,620кг</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="3" t="n">
+        <v>2821</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>361793.25</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>441387.77</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Сталь угловая 75*75, 75*75*7 сталь 3сп5, L = 6м -48кг</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="3" t="n">
+        <v>384</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>43948.8</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>53617.54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Стальной лист просечно-вытяжной 5.0 мм Ст.3 1000х2500, 5.0 мм Ст.3 1000х2500 (98кг)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="3" t="n">
+        <v>1568</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>202664</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>247250.08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Швеллер стальной горячекатанный 16, 16 С245 (12 п.м -170,400кг)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="3" t="n">
+        <v>1704</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>299205.36</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>365030.54</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>ИТОГО трубная часть</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
         <v>3.0603</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G12" s="9" t="n">
+        <v>161580.3</v>
+      </c>
+      <c r="H12" s="9" t="n">
         <v>494484.2</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="I12" s="9" t="n">
+        <v>197127.97</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>603270.72</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>ВСЕГО по лоту (трубы + прочее)</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>1484518.73</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>1811112.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="H14" s="9" t="n">
         <v>1484517.28</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>НМЦК с НДС 22% (справочно):</t>
         </is>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="J15" s="9" t="n">
         <v>1811111.08</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Трубная часть лота: 4 из 9 позиций; остальное — не трубы (сталь, стальной, швеллер, …), в таблицу не включено. ИТОГО — только трубная часть, «НМЦК из обоснования» — весь лот. Доля трубной части в НМЦК: 33.31 %.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Трубная часть лота: 4 из 9 позиций; остальное — не трубы (сталь, стальной, швеллер, …) — показано ниже отдельным блоком, без массы и цены за тонну. «ИТОГО трубная часть» — только трубы, «ВСЕГО по лоту» — все позиции. Доля трубной части в НМЦК: 33.31 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Ставка НДС в документах не указана, расчёт справочный по 22 %; закупка по 223-ФЗ, включать налоги в цену закон не требует — суммы взяты как в документе («без НДС»). «без НДС» — сумма из документа, «с НДС» = сумма × 1,22.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Источник: 10188 Извещение.docx</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
+    <row r="20"/>
+    <row r="21"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A12:B14"/>
+  <mergeCells count="2">
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A19:B21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
